--- a/p/ds_25/sql/topic-list_sql.xlsx
+++ b/p/ds_25/sql/topic-list_sql.xlsx
@@ -4,13 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12200" tabRatio="698" firstSheet="1" activeTab="3"/>
+    <workbookView windowWidth="28800" windowHeight="12200" tabRatio="698" firstSheet="1" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="bas" sheetId="18" r:id="rId1"/>
     <sheet name="core" sheetId="2" r:id="rId2"/>
     <sheet name="adv" sheetId="15" r:id="rId3"/>
     <sheet name="ex" sheetId="19" r:id="rId4"/>
+    <sheet name="-" sheetId="20" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -899,7 +900,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -908,7 +909,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1412,82 +1412,82 @@
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="7"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
+      <c r="A33" s="6"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
+      <c r="D33" s="6"/>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="7"/>
+      <c r="A34" s="6"/>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="7"/>
+      <c r="A35" s="6"/>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="7"/>
+      <c r="A36" s="6"/>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="7"/>
+      <c r="A38" s="6"/>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="8"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
+      <c r="A43" s="7"/>
+      <c r="B43" s="7"/>
+      <c r="C43" s="7"/>
     </row>
     <row r="53" spans="3:5">
-      <c r="C53" s="8"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
+      <c r="C53" s="7"/>
+      <c r="D53" s="7"/>
+      <c r="E53" s="7"/>
     </row>
     <row r="54" spans="3:5">
-      <c r="C54" s="8"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
+      <c r="C54" s="7"/>
+      <c r="D54" s="7"/>
+      <c r="E54" s="7"/>
     </row>
     <row r="55" spans="3:5">
-      <c r="C55" s="8"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
+      <c r="C55" s="7"/>
+      <c r="D55" s="7"/>
+      <c r="E55" s="7"/>
     </row>
     <row r="56" spans="3:5">
-      <c r="C56" s="8"/>
-      <c r="D56" s="8"/>
-      <c r="E56" s="8"/>
+      <c r="C56" s="7"/>
+      <c r="D56" s="7"/>
+      <c r="E56" s="7"/>
     </row>
     <row r="57" spans="3:5">
-      <c r="C57" s="8"/>
-      <c r="D57" s="8"/>
-      <c r="E57" s="8"/>
+      <c r="C57" s="7"/>
+      <c r="D57" s="7"/>
+      <c r="E57" s="7"/>
     </row>
     <row r="58" spans="3:5">
-      <c r="C58" s="8"/>
-      <c r="D58" s="8"/>
-      <c r="E58" s="8"/>
+      <c r="C58" s="7"/>
+      <c r="D58" s="7"/>
+      <c r="E58" s="7"/>
     </row>
     <row r="59" spans="3:5">
-      <c r="C59" s="8"/>
-      <c r="D59" s="8"/>
-      <c r="E59" s="8"/>
+      <c r="C59" s="7"/>
+      <c r="D59" s="7"/>
+      <c r="E59" s="7"/>
     </row>
     <row r="60" spans="3:5">
-      <c r="C60" s="8"/>
-      <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
+      <c r="C60" s="7"/>
+      <c r="D60" s="7"/>
+      <c r="E60" s="7"/>
     </row>
     <row r="61" spans="3:5">
-      <c r="C61" s="8"/>
-      <c r="D61" s="8"/>
-      <c r="E61" s="8"/>
+      <c r="C61" s="7"/>
+      <c r="D61" s="7"/>
+      <c r="E61" s="7"/>
     </row>
     <row r="62" spans="3:5">
-      <c r="C62" s="8"/>
-      <c r="D62" s="8"/>
-      <c r="E62" s="8"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="7"/>
+      <c r="E62" s="7"/>
     </row>
     <row r="63" spans="3:5">
-      <c r="C63" s="8"/>
-      <c r="D63" s="8"/>
-      <c r="E63" s="8"/>
+      <c r="C63" s="7"/>
+      <c r="D63" s="7"/>
+      <c r="E63" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1701,22 +1701,22 @@
       </c>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="7"/>
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
+      <c r="A44" s="6"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" s="7"/>
+      <c r="A45" s="6"/>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="7"/>
+      <c r="A46" s="6"/>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="7"/>
+      <c r="A47" s="6"/>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="7"/>
+      <c r="A49" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1913,7 +1913,7 @@
       <c r="C30"/>
       <c r="D30"/>
       <c r="E30"/>
-      <c r="I30" s="6"/>
+      <c r="I30" s="5"/>
     </row>
     <row r="31" ht="15.5" spans="1:9">
       <c r="A31"/>
@@ -1921,8 +1921,8 @@
       <c r="C31"/>
       <c r="D31"/>
       <c r="E31"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
     </row>
     <row r="32" ht="15.5" spans="1:9">
       <c r="A32"/>
@@ -1930,8 +1930,8 @@
       <c r="C32"/>
       <c r="D32"/>
       <c r="E32"/>
-      <c r="H32" s="6"/>
-      <c r="I32" s="6"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
     </row>
     <row r="33" ht="15.5" spans="1:9">
       <c r="A33"/>
@@ -1939,12 +1939,12 @@
       <c r="C33"/>
       <c r="D33"/>
       <c r="E33"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="6"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
     </row>
     <row r="34" spans="8:9">
-      <c r="H34" s="6"/>
-      <c r="I34" s="6"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2027,7 +2027,7 @@
     <row r="11" spans="1:6">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>75</v>
       </c>
       <c r="D11" s="4"/>
@@ -2113,7 +2113,7 @@
       <c r="C21"/>
       <c r="D21"/>
       <c r="E21"/>
-      <c r="I21" s="6"/>
+      <c r="I21" s="5"/>
     </row>
     <row r="22" ht="15.5" spans="1:9">
       <c r="A22"/>
@@ -2121,8 +2121,8 @@
       <c r="C22"/>
       <c r="D22"/>
       <c r="E22"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
     </row>
     <row r="23" ht="15.5" spans="1:9">
       <c r="A23"/>
@@ -2130,8 +2130,8 @@
       <c r="C23"/>
       <c r="D23"/>
       <c r="E23"/>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
     </row>
     <row r="24" ht="15.5" spans="1:9">
       <c r="A24"/>
@@ -2139,15 +2139,26 @@
       <c r="C24"/>
       <c r="D24"/>
       <c r="E24"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
     </row>
     <row r="25" spans="8:9">
-      <c r="H25" s="6"/>
-      <c r="I25" s="6"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="15.5"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/p/ds_25/sql/topic-list_sql.xlsx
+++ b/p/ds_25/sql/topic-list_sql.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12200" tabRatio="698" firstSheet="1" activeTab="4"/>
+    <workbookView windowWidth="20830" windowHeight="6600" tabRatio="698" firstSheet="1" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="bas" sheetId="18" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="79">
   <si>
     <t>Most basic things</t>
   </si>
@@ -126,6 +126,9 @@
     <t>Above basics</t>
   </si>
   <si>
+    <t>links</t>
+  </si>
+  <si>
     <t>context</t>
   </si>
   <si>
@@ -139,6 +142,32 @@
   </si>
   <si>
     <t>partition by</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">SELECT DISTINCT t.TGrp
+, AVG(s.Amt) </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t>OVER(PARTITION BY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Bahnschrift"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">  t.TGrp ) as 'GrpAvg' 
+FROM t  WHERE YEAR(s.OrderDate) = 2013    ORDER BY  1,2,3</t>
+    </r>
   </si>
   <si>
     <t>order by</t>
@@ -269,12 +298,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="26">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -294,6 +323,21 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Bahnschrift"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Bahnschrift"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <i/>
       <sz val="11"/>
       <color theme="1"/>
@@ -755,28 +799,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -785,122 +820,131 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -912,7 +956,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1412,82 +1461,82 @@
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="6"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
+      <c r="A33" s="8"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="8"/>
     </row>
     <row r="34" spans="1:1">
-      <c r="A34" s="6"/>
+      <c r="A34" s="8"/>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="6"/>
+      <c r="A35" s="8"/>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="6"/>
+      <c r="A36" s="8"/>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="6"/>
+      <c r="A38" s="8"/>
     </row>
     <row r="43" spans="1:3">
-      <c r="A43" s="7"/>
-      <c r="B43" s="7"/>
-      <c r="C43" s="7"/>
+      <c r="A43" s="10"/>
+      <c r="B43" s="10"/>
+      <c r="C43" s="10"/>
     </row>
     <row r="53" spans="3:5">
-      <c r="C53" s="7"/>
-      <c r="D53" s="7"/>
-      <c r="E53" s="7"/>
+      <c r="C53" s="10"/>
+      <c r="D53" s="10"/>
+      <c r="E53" s="10"/>
     </row>
     <row r="54" spans="3:5">
-      <c r="C54" s="7"/>
-      <c r="D54" s="7"/>
-      <c r="E54" s="7"/>
+      <c r="C54" s="10"/>
+      <c r="D54" s="10"/>
+      <c r="E54" s="10"/>
     </row>
     <row r="55" spans="3:5">
-      <c r="C55" s="7"/>
-      <c r="D55" s="7"/>
-      <c r="E55" s="7"/>
+      <c r="C55" s="10"/>
+      <c r="D55" s="10"/>
+      <c r="E55" s="10"/>
     </row>
     <row r="56" spans="3:5">
-      <c r="C56" s="7"/>
-      <c r="D56" s="7"/>
-      <c r="E56" s="7"/>
+      <c r="C56" s="10"/>
+      <c r="D56" s="10"/>
+      <c r="E56" s="10"/>
     </row>
     <row r="57" spans="3:5">
-      <c r="C57" s="7"/>
-      <c r="D57" s="7"/>
-      <c r="E57" s="7"/>
+      <c r="C57" s="10"/>
+      <c r="D57" s="10"/>
+      <c r="E57" s="10"/>
     </row>
     <row r="58" spans="3:5">
-      <c r="C58" s="7"/>
-      <c r="D58" s="7"/>
-      <c r="E58" s="7"/>
+      <c r="C58" s="10"/>
+      <c r="D58" s="10"/>
+      <c r="E58" s="10"/>
     </row>
     <row r="59" spans="3:5">
-      <c r="C59" s="7"/>
-      <c r="D59" s="7"/>
-      <c r="E59" s="7"/>
+      <c r="C59" s="10"/>
+      <c r="D59" s="10"/>
+      <c r="E59" s="10"/>
     </row>
     <row r="60" spans="3:5">
-      <c r="C60" s="7"/>
-      <c r="D60" s="7"/>
-      <c r="E60" s="7"/>
+      <c r="C60" s="10"/>
+      <c r="D60" s="10"/>
+      <c r="E60" s="10"/>
     </row>
     <row r="61" spans="3:5">
-      <c r="C61" s="7"/>
-      <c r="D61" s="7"/>
-      <c r="E61" s="7"/>
+      <c r="C61" s="10"/>
+      <c r="D61" s="10"/>
+      <c r="E61" s="10"/>
     </row>
     <row r="62" spans="3:5">
-      <c r="C62" s="7"/>
-      <c r="D62" s="7"/>
-      <c r="E62" s="7"/>
+      <c r="C62" s="10"/>
+      <c r="D62" s="10"/>
+      <c r="E62" s="10"/>
     </row>
     <row r="63" spans="3:5">
-      <c r="C63" s="7"/>
-      <c r="D63" s="7"/>
-      <c r="E63" s="7"/>
+      <c r="C63" s="10"/>
+      <c r="D63" s="10"/>
+      <c r="E63" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1499,17 +1548,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H49"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14" outlineLevelCol="7"/>
+  <dimension ref="A1:G50"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14" outlineLevelCol="6"/>
   <cols>
     <col min="1" max="1" width="27.3307692307692" style="1" customWidth="1"/>
     <col min="2" max="2" width="19.8307692307692" style="1" customWidth="1"/>
-    <col min="3" max="3" width="2.41538461538462" style="1" customWidth="1"/>
-    <col min="4" max="4" width="3.33076923076923" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.6692307692308" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.1692307692308" style="1" customWidth="1"/>
-    <col min="7" max="8" width="4.5" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="11" style="1"/>
+    <col min="3" max="3" width="1.93846153846154" style="6" customWidth="1"/>
+    <col min="4" max="6" width="1.93846153846154" style="1" customWidth="1"/>
+    <col min="7" max="7" width="49.6307692307692" style="1" customWidth="1"/>
+    <col min="8" max="16384" width="11" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:2">
@@ -1517,206 +1564,194 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="6" t="s">
         <v>3</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="3:7">
-      <c r="C3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G3" s="3"/>
-    </row>
-    <row r="4" spans="3:7">
-      <c r="C4" s="1" t="s">
+    </row>
+    <row r="3" spans="3:3">
+      <c r="C3" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="3"/>
-    </row>
-    <row r="5" spans="3:7">
-      <c r="C5" s="1" t="s">
+    </row>
+    <row r="4" spans="3:3">
+      <c r="C4" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="G5" s="3"/>
-    </row>
-    <row r="6" spans="4:7">
+    </row>
+    <row r="5" spans="3:3">
+      <c r="C5" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="4:4">
       <c r="D6" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G6" s="3"/>
-    </row>
-    <row r="7" spans="5:7">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="5:5">
       <c r="E7" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" s="3"/>
-    </row>
-    <row r="8" spans="5:7">
-      <c r="E8" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G8" s="3"/>
-    </row>
-    <row r="9" spans="5:7">
+    </row>
+    <row r="8" ht="42" spans="7:7">
+      <c r="G8" s="7" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="5:5">
       <c r="E9" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G9" s="3"/>
-    </row>
-    <row r="10" spans="5:7">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="5:5">
       <c r="E10" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G10" s="3"/>
-    </row>
-    <row r="11" spans="7:7">
-      <c r="G11" s="3"/>
-    </row>
-    <row r="12" spans="4:4">
-      <c r="D12" s="1" t="s">
         <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="5:5">
+      <c r="E11" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="4:4">
       <c r="D13" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14" spans="4:4">
       <c r="D14" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" spans="3:3">
-      <c r="C16" s="1" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="4:4">
-      <c r="D17" s="1" t="s">
+    <row r="15" spans="4:4">
+      <c r="D15" s="1" t="s">
         <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3">
+      <c r="C17" s="6" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="18" spans="4:4">
       <c r="D18" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="4:4">
       <c r="D19" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="21" spans="3:3">
-      <c r="C21" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22" spans="4:4">
-      <c r="D22" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="3:3">
-      <c r="C24" s="1" t="s">
+    <row r="20" spans="4:4">
+      <c r="D20" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="25" spans="4:4">
-      <c r="D25" s="1" t="s">
+    <row r="22" spans="3:3">
+      <c r="C22" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="4:4">
+      <c r="D23" s="1" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="27" spans="3:3">
-      <c r="C27" s="1" t="s">
+    <row r="25" spans="3:3">
+      <c r="C25" s="6" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="29" spans="3:3">
-      <c r="C29" s="1" t="s">
+    <row r="26" spans="4:4">
+      <c r="D26" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="30" spans="4:4">
-      <c r="D30" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="31" spans="2:5">
-      <c r="B31" s="1" t="s">
+    <row r="28" spans="3:3">
+      <c r="C28" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="E31" s="1" t="s">
+    </row>
+    <row r="30" spans="3:3">
+      <c r="C30" s="6" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="32" spans="4:4">
-      <c r="D32" s="4" t="s">
+    <row r="31" spans="4:4">
+      <c r="D31" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5">
+      <c r="B32" s="1" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="33" spans="2:5">
-      <c r="B33" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="D33" s="4"/>
-      <c r="E33" s="1" t="s">
+      <c r="E32" s="1" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="35" spans="3:3">
-      <c r="C35" s="1" t="s">
+    <row r="33" spans="4:4">
+      <c r="D33" s="4" t="s">
         <v>55</v>
       </c>
     </row>
+    <row r="34" spans="2:5">
+      <c r="B34" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D34" s="4"/>
+      <c r="E34" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
     <row r="36" spans="3:3">
-      <c r="C36" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="38" spans="3:3">
-      <c r="C38" s="1" t="s">
+      <c r="C36" s="6" t="s">
         <v>57</v>
       </c>
     </row>
+    <row r="37" spans="3:3">
+      <c r="C37" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
     <row r="39" spans="3:3">
-      <c r="C39" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" s="6"/>
-      <c r="B44" s="6"/>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6"/>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" s="6"/>
+      <c r="C39" s="6" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="40" spans="3:3">
+      <c r="C40" s="6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4">
+      <c r="A45" s="8"/>
+      <c r="B45" s="8"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="8"/>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" s="6"/>
+      <c r="A46" s="8"/>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" s="6"/>
-    </row>
-    <row r="49" spans="1:1">
-      <c r="A49" s="6"/>
+      <c r="A47" s="8"/>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="8"/>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1744,7 +1779,7 @@
   <sheetData>
     <row r="1" spans="2:2">
       <c r="B1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1769,52 +1804,52 @@
     </row>
     <row r="3" spans="3:3">
       <c r="C3" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="3:3">
       <c r="C5" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6" spans="3:3">
       <c r="C6" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="3:3">
       <c r="C7" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="3:3">
       <c r="C8" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" spans="3:3">
       <c r="C9" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="3:3">
       <c r="C10" s="1" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="11" spans="3:3">
       <c r="C11" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="3:3">
       <c r="C12" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13" spans="3:3">
       <c r="C13" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" ht="15.5" spans="3:3">
@@ -1971,7 +2006,7 @@
   <sheetData>
     <row r="1" spans="2:2">
       <c r="B1" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1999,22 +2034,22 @@
     </row>
     <row r="4" spans="3:3">
       <c r="C4" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="3:3">
       <c r="C6" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8" spans="3:3">
       <c r="C8" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="3:3">
       <c r="C9" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -2028,7 +2063,7 @@
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
@@ -2046,7 +2081,7 @@
       <c r="A13" s="4"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
